--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_rubber_tires.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.155</v>
+        <v>-0.212</v>
       </c>
       <c r="E2">
-        <v>0.0008699999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="G2">
-        <v>-0.4068678459937565</v>
+        <v>-0.8839285714285713</v>
       </c>
       <c r="H2">
-        <v>-0.4068678459937565</v>
+        <v>-0.8839285714285713</v>
       </c>
       <c r="I2">
-        <v>-0.5556711758584808</v>
+        <v>-1.06547619047619</v>
       </c>
       <c r="J2">
-        <v>-0.5556711758584808</v>
+        <v>-1.06547619047619</v>
       </c>
       <c r="K2">
-        <v>4.34</v>
+        <v>2.21</v>
       </c>
       <c r="L2">
-        <v>4.516129032258065</v>
+        <v>6.577380952380952</v>
       </c>
       <c r="M2">
-        <v>4.02</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>0.1028132992327366</v>
+        <v>0.08661417322834647</v>
       </c>
       <c r="O2">
-        <v>0.9262672811059908</v>
+        <v>0.497737556561086</v>
       </c>
       <c r="P2">
-        <v>4.02</v>
+        <v>1.1</v>
       </c>
       <c r="Q2">
-        <v>0.1028132992327366</v>
+        <v>0.08661417322834647</v>
       </c>
       <c r="R2">
-        <v>0.9262672811059908</v>
+        <v>0.497737556561086</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.469</v>
+        <v>1.55</v>
       </c>
       <c r="V2">
-        <v>0.01199488491048593</v>
+        <v>0.1220472440944882</v>
       </c>
       <c r="W2">
-        <v>0.1461279461279461</v>
+        <v>0.07491525423728813</v>
       </c>
       <c r="X2">
-        <v>0.1582067677869094</v>
+        <v>0.2908847086756955</v>
       </c>
       <c r="Y2">
-        <v>-0.01207882165896326</v>
+        <v>-0.2159694544384074</v>
       </c>
       <c r="Z2">
-        <v>0.03538421885930999</v>
+        <v>0.01137325254713469</v>
       </c>
       <c r="AA2">
-        <v>-0.01966199050038661</v>
+        <v>-0.01211792979724469</v>
       </c>
       <c r="AB2">
-        <v>0.1571437620199377</v>
+        <v>0.2886643496062679</v>
       </c>
       <c r="AC2">
-        <v>-0.1768057525203243</v>
+        <v>-0.3007822794035125</v>
       </c>
       <c r="AD2">
-        <v>0.512</v>
+        <v>0.213</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.512</v>
+        <v>0.213</v>
       </c>
       <c r="AG2">
-        <v>0.04300000000000004</v>
+        <v>-1.337</v>
       </c>
       <c r="AH2">
-        <v>0.01292537614864183</v>
+        <v>0.01649500503368698</v>
       </c>
       <c r="AI2">
-        <v>0.01705984272957484</v>
+        <v>0.01223224028025039</v>
       </c>
       <c r="AJ2">
-        <v>0.001098536136729429</v>
+        <v>-0.1176625891049899</v>
       </c>
       <c r="AK2">
-        <v>0.001455505534305928</v>
+        <v>-0.08428418331967472</v>
       </c>
       <c r="AL2">
-        <v>0.03</v>
+        <v>0.038</v>
       </c>
       <c r="AM2">
-        <v>-0.165</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="AN2">
-        <v>-1.101075268817204</v>
+        <v>-0.6938110749185668</v>
       </c>
       <c r="AO2">
-        <v>-17.8</v>
+        <v>-9.421052631578947</v>
       </c>
       <c r="AP2">
-        <v>-0.09247311827956997</v>
+        <v>4.355048859934853</v>
       </c>
       <c r="AQ2">
-        <v>3.236363636363636</v>
+        <v>4.837837837837837</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.155</v>
+        <v>-0.212</v>
       </c>
       <c r="E3">
-        <v>0.0008699999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="G3">
-        <v>-0.4068678459937565</v>
+        <v>-0.8839285714285713</v>
       </c>
       <c r="H3">
-        <v>-0.4068678459937565</v>
+        <v>-0.8839285714285713</v>
       </c>
       <c r="I3">
-        <v>-0.5556711758584808</v>
+        <v>-1.06547619047619</v>
       </c>
       <c r="J3">
-        <v>-0.5556711758584808</v>
+        <v>-1.06547619047619</v>
       </c>
       <c r="K3">
-        <v>4.34</v>
+        <v>2.21</v>
       </c>
       <c r="L3">
-        <v>4.516129032258065</v>
+        <v>6.577380952380952</v>
       </c>
       <c r="M3">
-        <v>4.02</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>0.1028132992327366</v>
+        <v>0.08661417322834647</v>
       </c>
       <c r="O3">
-        <v>0.9262672811059908</v>
+        <v>0.497737556561086</v>
       </c>
       <c r="P3">
-        <v>4.02</v>
+        <v>1.1</v>
       </c>
       <c r="Q3">
-        <v>0.1028132992327366</v>
+        <v>0.08661417322834647</v>
       </c>
       <c r="R3">
-        <v>0.9262672811059908</v>
+        <v>0.497737556561086</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.469</v>
+        <v>1.55</v>
       </c>
       <c r="V3">
-        <v>0.01199488491048593</v>
+        <v>0.1220472440944882</v>
       </c>
       <c r="W3">
-        <v>0.1461279461279461</v>
+        <v>0.07491525423728813</v>
       </c>
       <c r="X3">
-        <v>0.1582067677869094</v>
+        <v>0.2908847086756955</v>
       </c>
       <c r="Y3">
-        <v>-0.01207882165896326</v>
+        <v>-0.2159694544384074</v>
       </c>
       <c r="Z3">
-        <v>0.03538421885930999</v>
+        <v>0.01137325254713469</v>
       </c>
       <c r="AA3">
-        <v>-0.01966199050038661</v>
+        <v>-0.01211792979724469</v>
       </c>
       <c r="AB3">
-        <v>0.1571437620199377</v>
+        <v>0.2886643496062679</v>
       </c>
       <c r="AC3">
-        <v>-0.1768057525203243</v>
+        <v>-0.3007822794035125</v>
       </c>
       <c r="AD3">
-        <v>0.512</v>
+        <v>0.213</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.512</v>
+        <v>0.213</v>
       </c>
       <c r="AG3">
-        <v>0.04300000000000004</v>
+        <v>-1.337</v>
       </c>
       <c r="AH3">
-        <v>0.01292537614864183</v>
+        <v>0.01649500503368698</v>
       </c>
       <c r="AI3">
-        <v>0.01705984272957484</v>
+        <v>0.01223224028025039</v>
       </c>
       <c r="AJ3">
-        <v>0.001098536136729429</v>
+        <v>-0.1176625891049899</v>
       </c>
       <c r="AK3">
-        <v>0.001455505534305928</v>
+        <v>-0.08428418331967472</v>
       </c>
       <c r="AL3">
-        <v>0.03</v>
+        <v>0.038</v>
       </c>
       <c r="AM3">
-        <v>-0.165</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="AN3">
-        <v>-1.101075268817204</v>
+        <v>-0.6938110749185668</v>
       </c>
       <c r="AO3">
-        <v>-17.8</v>
+        <v>-9.421052631578947</v>
       </c>
       <c r="AP3">
-        <v>-0.09247311827956997</v>
+        <v>4.355048859934853</v>
       </c>
       <c r="AQ3">
-        <v>3.236363636363636</v>
+        <v>4.837837837837837</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_rubber_tires.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_rubber_tires.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.212</v>
+        <v>-0.765</v>
       </c>
       <c r="E2">
-        <v>0.121</v>
+        <v>-0.0274</v>
       </c>
       <c r="G2">
-        <v>-0.8839285714285713</v>
+        <v>-424</v>
       </c>
       <c r="H2">
-        <v>-0.8839285714285713</v>
+        <v>-424</v>
       </c>
       <c r="I2">
-        <v>-1.06547619047619</v>
+        <v>-387</v>
       </c>
       <c r="J2">
-        <v>-1.06547619047619</v>
+        <v>-359.6550898203593</v>
       </c>
       <c r="K2">
-        <v>2.21</v>
+        <v>1.56</v>
       </c>
       <c r="L2">
-        <v>6.577380952380952</v>
+        <v>1560</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="N2">
-        <v>0.08661417322834647</v>
+        <v>0.0791139240506329</v>
       </c>
       <c r="O2">
-        <v>0.497737556561086</v>
+        <v>0.8012820512820512</v>
       </c>
       <c r="P2">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
-        <v>0.08661417322834647</v>
+        <v>0.0791139240506329</v>
       </c>
       <c r="R2">
-        <v>0.497737556561086</v>
+        <v>0.8012820512820512</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.55</v>
+        <v>0.124</v>
       </c>
       <c r="V2">
-        <v>0.1220472440944882</v>
+        <v>0.007848101265822784</v>
       </c>
       <c r="W2">
-        <v>0.07491525423728813</v>
+        <v>0.09069767441860466</v>
       </c>
       <c r="X2">
-        <v>0.2908847086756955</v>
+        <v>0.2288982906492202</v>
       </c>
       <c r="Y2">
-        <v>-0.2159694544384074</v>
+        <v>-0.1382006162306156</v>
       </c>
       <c r="Z2">
-        <v>0.01137325254713469</v>
+        <v>6.303977809998108e-05</v>
       </c>
       <c r="AA2">
-        <v>-0.01211792979724469</v>
+        <v>-0.02267257705480422</v>
       </c>
       <c r="AB2">
-        <v>0.2886643496062679</v>
+        <v>0.2284283554620881</v>
       </c>
       <c r="AC2">
-        <v>-0.3007822794035125</v>
+        <v>-0.2511009325168923</v>
       </c>
       <c r="AD2">
-        <v>0.213</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.213</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AG2">
-        <v>-1.337</v>
+        <v>-0.03999999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.01649500503368698</v>
+        <v>0.005288340468395871</v>
       </c>
       <c r="AI2">
-        <v>0.01223224028025039</v>
+        <v>0.004267425320056899</v>
       </c>
       <c r="AJ2">
-        <v>-0.1176625891049899</v>
+        <v>-0.002538071065989847</v>
       </c>
       <c r="AK2">
-        <v>-0.08428418331967472</v>
+        <v>-0.002044989775051124</v>
       </c>
       <c r="AL2">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AM2">
-        <v>-0.07400000000000001</v>
+        <v>-0.5389999999999999</v>
       </c>
       <c r="AN2">
-        <v>-0.6938110749185668</v>
+        <v>-0.228882833787466</v>
       </c>
       <c r="AO2">
-        <v>-9.421052631578947</v>
+        <v>-10.75</v>
       </c>
       <c r="AP2">
-        <v>4.355048859934853</v>
+        <v>0.108991825613079</v>
       </c>
       <c r="AQ2">
-        <v>4.837837837837837</v>
+        <v>0.7179962894248609</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.212</v>
+        <v>-0.765</v>
       </c>
       <c r="E3">
-        <v>0.121</v>
+        <v>-0.0274</v>
       </c>
       <c r="G3">
-        <v>-0.8839285714285713</v>
+        <v>-424</v>
       </c>
       <c r="H3">
-        <v>-0.8839285714285713</v>
+        <v>-424</v>
       </c>
       <c r="I3">
-        <v>-1.06547619047619</v>
+        <v>-387</v>
       </c>
       <c r="J3">
-        <v>-1.06547619047619</v>
+        <v>-359.6550898203593</v>
       </c>
       <c r="K3">
-        <v>2.21</v>
+        <v>1.56</v>
       </c>
       <c r="L3">
-        <v>6.577380952380952</v>
+        <v>1560</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="N3">
-        <v>0.08661417322834647</v>
+        <v>0.0791139240506329</v>
       </c>
       <c r="O3">
-        <v>0.497737556561086</v>
+        <v>0.8012820512820512</v>
       </c>
       <c r="P3">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>0.08661417322834647</v>
+        <v>0.0791139240506329</v>
       </c>
       <c r="R3">
-        <v>0.497737556561086</v>
+        <v>0.8012820512820512</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.55</v>
+        <v>0.124</v>
       </c>
       <c r="V3">
-        <v>0.1220472440944882</v>
+        <v>0.007848101265822784</v>
       </c>
       <c r="W3">
-        <v>0.07491525423728813</v>
+        <v>0.09069767441860466</v>
       </c>
       <c r="X3">
-        <v>0.2908847086756955</v>
+        <v>0.2288982906492202</v>
       </c>
       <c r="Y3">
-        <v>-0.2159694544384074</v>
+        <v>-0.1382006162306156</v>
       </c>
       <c r="Z3">
-        <v>0.01137325254713469</v>
+        <v>6.303977809998108e-05</v>
       </c>
       <c r="AA3">
-        <v>-0.01211792979724469</v>
+        <v>-0.02267257705480422</v>
       </c>
       <c r="AB3">
-        <v>0.2886643496062679</v>
+        <v>0.2284283554620881</v>
       </c>
       <c r="AC3">
-        <v>-0.3007822794035125</v>
+        <v>-0.2511009325168923</v>
       </c>
       <c r="AD3">
-        <v>0.213</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.213</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AG3">
-        <v>-1.337</v>
+        <v>-0.03999999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.01649500503368698</v>
+        <v>0.005288340468395871</v>
       </c>
       <c r="AI3">
-        <v>0.01223224028025039</v>
+        <v>0.004267425320056899</v>
       </c>
       <c r="AJ3">
-        <v>-0.1176625891049899</v>
+        <v>-0.002538071065989847</v>
       </c>
       <c r="AK3">
-        <v>-0.08428418331967472</v>
+        <v>-0.002044989775051124</v>
       </c>
       <c r="AL3">
-        <v>0.038</v>
+        <v>0.036</v>
       </c>
       <c r="AM3">
-        <v>-0.07400000000000001</v>
+        <v>-0.5389999999999999</v>
       </c>
       <c r="AN3">
-        <v>-0.6938110749185668</v>
+        <v>-0.228882833787466</v>
       </c>
       <c r="AO3">
-        <v>-9.421052631578947</v>
+        <v>-10.75</v>
       </c>
       <c r="AP3">
-        <v>4.355048859934853</v>
+        <v>0.108991825613079</v>
       </c>
       <c r="AQ3">
-        <v>4.837837837837837</v>
+        <v>0.7179962894248609</v>
       </c>
     </row>
   </sheetData>
